--- a/docs/downloads/经营分_鲁东省区__烟台片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__烟台片区_2026-10-18.xlsx
@@ -1299,33 +1299,33 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7008060662844786695</t>
+          <t>7515989685458438163</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（烟台八角湾国际会展中心店)</t>
+          <t>维也纳国际酒店（经典版烟台福山区永达街万达广场店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(烟台八角湾国际会展中心店)</t>
+          <t>维也纳国际酒店(烟台福山区永达街店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1335,19 +1335,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1387,22 +1387,22 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601130735074019335</t>
+          <t>7008060662844786695</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>维也纳酒店（莱州朗湖国际广场店）</t>
+          <t>维也纳3好酒店（烟台八角湾国际会展中心店)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>维也纳酒店(莱州朗湖国际广场店)</t>
+          <t>维也纳3好酒店(烟台八角湾国际会展中心店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601185063352666120</t>
+          <t>6601130735074019335</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>锦江之星品尚(烟台开发区五指山路店)</t>
+          <t>维也纳酒店（莱州朗湖国际广场店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>锦江之星品尚酒店(烟台开发区五指山路店)</t>
+          <t>维也纳酒店(莱州朗湖国际广场店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1497,7 +1497,7 @@
         <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1563,17 +1563,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7234785163874404385</t>
+          <t>6601185063352666120</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>锦江都城招远开发区黄金珠宝首饰城酒店</t>
+          <t>锦江之星品尚(烟台开发区五指山路店)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>锦江都城酒店(招远开发区黄金珠宝首饰城店)</t>
+          <t>锦江之星品尚酒店(烟台开发区五指山路店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1582,18 +1582,18 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -1605,7 +1605,7 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7515989685458438163</t>
+          <t>7234785163874404385</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（经典版烟台福山区永达街万达广场店）</t>
+          <t>锦江都城招远开发区黄金珠宝首饰城酒店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(烟台福山区永达街店)</t>
+          <t>锦江都城酒店(招远开发区黄金珠宝首饰城店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1670,30 +1670,30 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
@@ -2003,17 +2003,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601145381013161987</t>
+          <t>6601164048903964685</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>锦江之星（烟台万达广场所城里店）</t>
+          <t>锦江之星风尚（烟台蓬莱市蓬莱阁酒店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>锦江之星(烟台万达广场环山路店)</t>
+          <t>锦江之星酒店(烟台蓬莱区蓬莱阁店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2045,13 +2045,13 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2091,33 +2091,33 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7645912169418065972</t>
+          <t>6601145381013161987</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>麗枫酒店（烟台站吾悦广场店）</t>
+          <t>锦江之星（烟台万达广场所城里店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>麗枫酒店(烟台站吾悦广场店)</t>
+          <t>锦江之星(烟台万达广场环山路店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2127,19 +2127,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2179,33 +2179,33 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7386103113658140711</t>
+          <t>7645912169418065972</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(烟台蓬莱欧乐堡海水浴场店)</t>
+          <t>麗枫酒店（烟台站吾悦广场店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>白玉兰酒店(烟台蓬莱欧乐堡海水浴场店)</t>
+          <t>麗枫酒店(烟台站吾悦广场店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I19" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2215,13 +2215,13 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6601137999038121987</t>
+          <t>7234811897537628160</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（烟台金沙滩海水浴场振华购物中心店）</t>
+          <t>IU酒店（烟台开发区金沙滩海水浴场店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(烟台金沙滩海水浴场振华购物中心店)</t>
+          <t>IU酒店(烟台开发区金沙滩海水浴场店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2309,13 +2309,13 @@
         <v>30</v>
       </c>
       <c r="O20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="n">
         <v>25</v>
-      </c>
-      <c r="P20" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7363871407082342435</t>
+          <t>7386103113658140711</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0烟台蓬莱阁海水浴场店）</t>
+          <t>白玉兰商务酒店(烟台蓬莱欧乐堡海水浴场店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0烟台蓬莱阁店)</t>
+          <t>白玉兰酒店(烟台蓬莱欧乐堡海水浴场店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2443,17 +2443,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6668531909951260686</t>
+          <t>6601137999038121987</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳酒店（烟台高铁南站店）</t>
+          <t>维也纳国际酒店（烟台金沙滩海水浴场振华购物中心店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳酒店(烟台高铁南站店)</t>
+          <t>维也纳国际酒店(烟台金沙滩海水浴场振华购物中心店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2465,7 +2465,7 @@
         <v>105</v>
       </c>
       <c r="I22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6601164048903964685</t>
+          <t>7363871407082342435</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>锦江之星风尚（烟台蓬莱市蓬莱阁酒店）</t>
+          <t>维也纳酒店（5.0烟台蓬莱阁海水浴场店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>锦江之星酒店(烟台蓬莱区蓬莱阁店)</t>
+          <t>维也纳酒店(5.0烟台蓬莱阁店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2553,11 +2553,11 @@
         <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2567,13 +2567,13 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
+        <v>30</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
         <v>25</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30</v>
-      </c>
-      <c r="O23" t="n">
-        <v>30</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
@@ -2619,17 +2619,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601151347754534920</t>
+          <t>6668531909951260686</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7天酒店（烟台蓬莱阁景区海水浴场登州路店）</t>
+          <t>维也纳酒店（烟台高铁南站店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7天酒店(烟台蓬莱阁景区海水浴场登州路店)</t>
+          <t>维也纳酒店(烟台高铁南站店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2707,29 +2707,29 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7234811897537628160</t>
+          <t>6601151347754534920</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IU酒店（烟台开发区金沙滩海水浴场店）</t>
+          <t>7天酒店（烟台蓬莱阁景区海水浴场登州路店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IU酒店(烟台开发区金沙滩海水浴场店)</t>
+          <t>7天酒店(烟台蓬莱阁景区海水浴场登州路店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>110</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
